--- a/output/pdf_financials_xlsx/NRX.xlsx
+++ b/output/pdf_financials_xlsx/NRX.xlsx
@@ -967,34 +967,34 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.039148</v>
+        <v>-0.039148</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.821506</v>
+        <v>-0.821506</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.136049</v>
+        <v>-0.136049</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.08576300000000001</v>
+        <v>-0.08576300000000001</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.027771</v>
+        <v>-0.027771</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.647</v>
+        <v>-1.647</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>8.169</v>
+        <v>-8.169</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.639</v>
+        <v>-3.639</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.043</v>
+        <v>-5.043</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>6.384</v>
+        <v>-6.384</v>
       </c>
     </row>
     <row r="17">
@@ -1155,34 +1155,34 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.039148</v>
+        <v>-0.039148</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.821506</v>
+        <v>-0.821506</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.136049</v>
+        <v>-0.136049</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.08576300000000001</v>
+        <v>-0.08576300000000001</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.027771</v>
+        <v>-0.027771</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.647</v>
+        <v>-1.647</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>8.169</v>
+        <v>-8.169</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.639</v>
+        <v>-3.639</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.043</v>
+        <v>-5.043</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>6.384</v>
+        <v>-6.384</v>
       </c>
     </row>
     <row r="21">
@@ -1266,34 +1266,34 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.039148</v>
+        <v>-0.039148</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.821506</v>
+        <v>-0.821506</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.136049</v>
+        <v>-0.136049</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.08576300000000001</v>
+        <v>-0.08576300000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.027771</v>
+        <v>-0.027771</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.647</v>
+        <v>-1.647</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.169</v>
+        <v>-8.169</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>3.639</v>
+        <v>-3.639</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.043</v>
+        <v>-5.043</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.384</v>
+        <v>-6.384</v>
       </c>
     </row>
     <row r="24">
@@ -1426,16 +1426,16 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>16.47</v>
+        <v>-16.47</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>37.819444</v>
+        <v>-37.819444</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>44.925926</v>
+        <v>-44.925926</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>65.493506</v>
+        <v>-65.493506</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.039148</v>
+        <v>-0.039148</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.821506</v>
+        <v>-0.821506</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.136049</v>
+        <v>-0.136049</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.08576300000000001</v>
+        <v>-0.08576300000000001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.027771</v>
+        <v>-0.027771</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.647</v>
+        <v>-1.647</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8.169</v>
+        <v>-8.169</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.639</v>
+        <v>-3.639</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.043</v>
+        <v>-5.043</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.384</v>
+        <v>-6.384</v>
       </c>
     </row>
     <row r="28">
@@ -1524,34 +1524,34 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.039148</v>
+        <v>-0.039148</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.821506</v>
+        <v>-0.821506</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.136049</v>
+        <v>-0.136049</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.08576300000000001</v>
+        <v>-0.08576300000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.027771</v>
+        <v>-0.027771</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.647</v>
+        <v>-1.647</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8.175000000000001</v>
+        <v>-8.163</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.672</v>
+        <v>-3.606</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.043</v>
+        <v>-5.043</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.384</v>
+        <v>-6.384</v>
       </c>
     </row>
     <row r="30">
@@ -1618,34 +1618,34 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3925,19 +3925,19 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.073</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.045</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.202</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="92">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.027194</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.054375</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -3962,19 +3962,19 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.337</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.992</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>19.466</v>
+        <v>21.063</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>26.092</v>
+        <v>28.209</v>
       </c>
     </row>
     <row r="93">
@@ -4186,13 +4186,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.039148</v>
+        <v>-0.039148</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.821506</v>
+        <v>-0.821506</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.136049</v>
+        <v>-0.136049</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.08576300000000001</v>
@@ -7276,7 +7276,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -7340,7 +7344,11 @@
           <t>Share-based payment reserve 14</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -8126,7 +8134,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -8190,7 +8202,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -9114,7 +9130,11 @@
           <t>Warrants reserve 12</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -9178,7 +9198,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -9242,7 +9266,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -11328,7 +11356,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -11394,7 +11426,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -11458,7 +11494,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -13024,7 +13064,11 @@
           <t>Warrants reserve (note 8 (e))</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -13694,7 +13738,11 @@
           <t>Warrants reserve (Note 8e)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>0.027194</v>
       </c>
@@ -23091,13 +23139,13 @@
         </is>
       </c>
       <c r="L268" s="5" t="n">
-        <v>3.639</v>
+        <v>-3.639</v>
       </c>
       <c r="M268" s="5" t="n">
-        <v>5.043</v>
+        <v>-5.043</v>
       </c>
       <c r="N268" s="5" t="n">
-        <v>6.384</v>
+        <v>-6.384</v>
       </c>
     </row>
     <row r="269">
@@ -24167,10 +24215,10 @@
         </is>
       </c>
       <c r="J285" s="5" t="n">
-        <v>1.647</v>
+        <v>-1.647</v>
       </c>
       <c r="K285" s="5" t="n">
-        <v>8.169</v>
+        <v>-8.169</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -25002,10 +25050,10 @@
         </is>
       </c>
       <c r="I298" s="5" t="n">
-        <v>0.027771</v>
+        <v>-0.027771</v>
       </c>
       <c r="J298" s="5" t="n">
-        <v>0.165634</v>
+        <v>-0.165634</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -25577,10 +25625,10 @@
         </is>
       </c>
       <c r="H307" s="5" t="n">
-        <v>0.08576300000000001</v>
+        <v>-0.08576300000000001</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>0.027771</v>
+        <v>-0.027771</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -26223,10 +26271,10 @@
         </is>
       </c>
       <c r="F317" s="5" t="n">
-        <v>0.821506</v>
+        <v>-0.821506</v>
       </c>
       <c r="G317" s="5" t="n">
-        <v>0.136049</v>
+        <v>-0.136049</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -26750,10 +26798,10 @@
         </is>
       </c>
       <c r="E325" s="5" t="n">
-        <v>0.039148</v>
+        <v>-0.039148</v>
       </c>
       <c r="F325" s="5" t="n">
-        <v>0.821506</v>
+        <v>-0.821506</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NRX.xlsx
+++ b/output/pdf_financials_xlsx/NRX.xlsx
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.411208</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.215233</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.038894</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002244</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.008638</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>2.214</v>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.411208</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.215233</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.038894</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002244</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.008638</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>2.214</v>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.787442</v>
+        <v>0.376234</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.29409</v>
+        <v>0.078857</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.052547</v>
+        <v>0.013653</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.035843</v>
+        <v>0.033599</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.017765</v>
+        <v>0.009127</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.47</v>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">

--- a/output/pdf_financials_xlsx/NRX.xlsx
+++ b/output/pdf_financials_xlsx/NRX.xlsx
@@ -4269,13 +4269,13 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005609</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.009471</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000565</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>-0.01</v>
@@ -4454,13 +4454,13 @@
         <v>-0.116773</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.021463</v>
+        <v>-0.027072</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.0016</v>
+        <v>0.011071</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07038800000000001</v>
+        <v>0.069823</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>-0.01</v>
@@ -4509,7 +4509,7 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="108">
@@ -14002,7 +14002,11 @@
           <t>Share-based compensation expenses</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -17718,7 +17722,11 @@
           <t>Proceeds from the issuance of private placement</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -20084,7 +20092,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
